--- a/excel_reports/backtest_compare/s3/compare_s3_M15_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s3/compare_s3_M15_20260528_0800_20260608_1000.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 19:32:04</t>
+          <t>2026-06-18 16:58:31</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
         <v>46175.11458333334</v>
       </c>
       <c r="AF21" s="12" t="n">
-        <v>4464.89</v>
+        <v>4464.91</v>
       </c>
       <c r="AG21" s="12" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>4465.05</v>
       </c>
       <c r="AI21" s="12" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="AJ21" s="12" t="inlineStr"/>
       <c r="AK21" s="12" t="inlineStr"/>
@@ -9169,7 +9169,7 @@
         <v>46175.11458333334</v>
       </c>
       <c r="AF6" s="12" t="n">
-        <v>4464.89</v>
+        <v>4464.91</v>
       </c>
       <c r="AG6" s="12" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>4465.05</v>
       </c>
       <c r="AI6" s="12" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="AJ6" s="12" t="inlineStr"/>
       <c r="AK6" s="12" t="inlineStr"/>
@@ -12238,7 +12238,7 @@
         <v>5</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>-51.38</v>
+        <v>-51.4</v>
       </c>
       <c r="F12" s="15" t="n">
         <v>46174.91666666666</v>
@@ -12620,7 +12620,7 @@
         <v>17</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>137.74</v>
+        <v>137.72</v>
       </c>
       <c r="F26" s="15" t="n">
         <v>46170.51041666666</v>
@@ -13113,7 +13113,7 @@
         <v>13</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>143.99</v>
+        <v>143.97</v>
       </c>
       <c r="F43" s="15" t="n">
         <v>46171.33333333334</v>

--- a/excel_reports/backtest_compare/s3/compare_s3_M15_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s3/compare_s3_M15_20260528_0800_20260608_1000.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Live Only'!$A$1:$BK$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Matches'!$A$1:$BK$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -520,7 +520,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-18 16:58:31</t>
+          <t>2026-06-19 17:38:31</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
         <v>46175.11458333334</v>
       </c>
       <c r="AF21" s="12" t="n">
-        <v>4464.91</v>
+        <v>4464.89</v>
       </c>
       <c r="AG21" s="12" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>4465.05</v>
       </c>
       <c r="AI21" s="12" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="AJ21" s="12" t="inlineStr"/>
       <c r="AK21" s="12" t="inlineStr"/>
@@ -9169,7 +9169,7 @@
         <v>46175.11458333334</v>
       </c>
       <c r="AF6" s="12" t="n">
-        <v>4464.91</v>
+        <v>4464.89</v>
       </c>
       <c r="AG6" s="12" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>4465.05</v>
       </c>
       <c r="AI6" s="12" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="AJ6" s="12" t="inlineStr"/>
       <c r="AK6" s="12" t="inlineStr"/>
@@ -11879,7 +11879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -12238,7 +12238,7 @@
         <v>5</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>-51.4</v>
+        <v>-51.38</v>
       </c>
       <c r="F12" s="15" t="n">
         <v>46174.91666666666</v>
@@ -12620,7 +12620,7 @@
         <v>17</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>137.72</v>
+        <v>137.74</v>
       </c>
       <c r="F26" s="15" t="n">
         <v>46170.51041666666</v>
@@ -13035,240 +13035,8 @@
         <v>46171.15751157407</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="14" t="inlineStr">
-        <is>
-          <t>live_s14_family</t>
-        </is>
-      </c>
-      <c r="B41" s="14" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D41" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="E41" s="14" t="n">
-        <v>-30.95</v>
-      </c>
-      <c r="F41" s="15" t="n">
-        <v>46170.37732638889</v>
-      </c>
-      <c r="G41" s="15" t="n">
-        <v>46175.29211805556</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>live_s14_family</t>
-        </is>
-      </c>
-      <c r="B42" s="14" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D42" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="E42" s="14" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="F42" s="15" t="n">
-        <v>46170.53115740741</v>
-      </c>
-      <c r="G42" s="15" t="n">
-        <v>46171.57872685185</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B43" s="14" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>13</v>
-      </c>
-      <c r="E43" s="14" t="n">
-        <v>143.97</v>
-      </c>
-      <c r="F43" s="15" t="n">
-        <v>46171.33333333334</v>
-      </c>
-      <c r="G43" s="15" t="n">
-        <v>46181.33333333334</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="14" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B44" s="14" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D44" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="E44" s="14" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="F44" s="15" t="n">
-        <v>46170.51041666666</v>
-      </c>
-      <c r="G44" s="15" t="n">
-        <v>46178.48958333334</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="14" t="inlineStr">
-        <is>
-          <t>mismatch_s14_family</t>
-        </is>
-      </c>
-      <c r="B45" s="14" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D45" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="E45" s="14" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="F45" s="15" t="n">
-        <v>46170.9068287037</v>
-      </c>
-      <c r="G45" s="15" t="n">
-        <v>46174.50113425926</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="14" t="inlineStr">
-        <is>
-          <t>mismatch_s14_family</t>
-        </is>
-      </c>
-      <c r="B46" s="14" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D46" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="14" t="n">
-        <v>30.48</v>
-      </c>
-      <c r="F46" s="15" t="n">
-        <v>46174.65696759259</v>
-      </c>
-      <c r="G46" s="15" t="n">
-        <v>46174.65696759259</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="14" t="inlineStr">
-        <is>
-          <t>s14_family_mismatch</t>
-        </is>
-      </c>
-      <c r="B47" s="14" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D47" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="E47" s="14" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="F47" s="15" t="n">
-        <v>46170.9068287037</v>
-      </c>
-      <c r="G47" s="15" t="n">
-        <v>46174.50113425926</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="14" t="inlineStr">
-        <is>
-          <t>s14_family_mismatch</t>
-        </is>
-      </c>
-      <c r="B48" s="14" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="14" t="n">
-        <v>30.48</v>
-      </c>
-      <c r="F48" s="15" t="n">
-        <v>46174.65696759259</v>
-      </c>
-      <c r="G48" s="15" t="n">
-        <v>46174.65696759259</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G48"/>
+  <autoFilter ref="A1:G40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/excel_reports/backtest_compare/s3/compare_s3_M15_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s3/compare_s3_M15_20260528_0800_20260608_1000.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-19 17:38:31</t>
+          <t>2026-06-19 17:54:49</t>
         </is>
       </c>
     </row>

--- a/excel_reports/backtest_compare/s3/compare_s3_M15_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s3/compare_s3_M15_20260528_0800_20260608_1000.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-19 17:54:49</t>
+          <t>2026-06-21 19:01:43</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>CLOSE_LIFECYCLE_PD</t>
+          <t>LIVE_HISTORICAL_PD_SKIP_DRIFT</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_HISTORICAL_PD_SKIP_DRIFT:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -5739,7 +5739,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>CLOSE_LIFECYCLE_PD</t>
+          <t>LIVE_HISTORICAL_PD_SKIP_DRIFT</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_HISTORICAL_PD_SKIP_DRIFT:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_HISTORICAL_PD_SKIP_DRIFT:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>CLOSE_LIFECYCLE_PD</t>
+          <t>LIVE_HISTORICAL_PD_SKIP_DRIFT</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
